--- a/AAII_Financials/Yearly/KYTX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KYTX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="92">
   <si>
     <t>KYTX</t>
   </si>
@@ -753,11 +753,11 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>133700</v>
-      </c>
-      <c r="E9" s="3">
-        <v>112500</v>
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F9" s="3">
         <v>49900</v>
@@ -789,11 +789,11 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>-133700</v>
-      </c>
-      <c r="E10" s="3">
-        <v>-112500</v>
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F10" s="3">
         <v>-49900</v>
